--- a/pensum/ma10/MA10_Markedsplanen_oppsummert_Regneark_Markedsplanen_i_tall.xlsx
+++ b/pensum/ma10/MA10_Markedsplanen_oppsummert_Regneark_Markedsplanen_i_tall.xlsx
@@ -1083,7 +1083,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1234,6 +1234,14 @@
     </xf>
     <xf numFmtId="169" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1524,7 +1532,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1659,7 +1667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
@@ -1951,8 +1959,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+    <row ht="27" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A33" t="s">
         <v>79</v>
       </c>
       <c r="B33" s="22" t="s">
@@ -2086,7 +2094,7 @@
       <c r="B5" s="24" t="n">
         <v>51360</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c s="38" r="C5" t="s">
         <v>100</v>
       </c>
       <c r="D5" s="24" t="n">
@@ -2103,7 +2111,7 @@
       <c r="B6" s="24" t="n">
         <v>8830</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c s="38" r="C6" t="s">
         <v>100</v>
       </c>
       <c r="D6" s="24" t="n">
@@ -2375,7 +2383,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c s="39" r="A4" t="s">
         <v>130</v>
       </c>
       <c r="B4" s="20" t="s">
@@ -2420,11 +2428,11 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c s="38" r="B7" t="s">
         <v>143</v>
       </c>
       <c r="C7" s="25" t="n">
@@ -2447,11 +2455,11 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c s="38" r="B8" t="s">
         <v>147</v>
       </c>
       <c r="C8" s="25" t="n">
@@ -2474,11 +2482,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c s="38" r="B9" t="s">
         <v>151</v>
       </c>
       <c r="C9" s="25" t="n">
@@ -2501,11 +2509,11 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c s="38" r="B10" t="s">
         <v>155</v>
       </c>
       <c r="C10" s="25" t="n">
@@ -2528,11 +2536,11 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c s="38" r="B11" t="s">
         <v>159</v>
       </c>
       <c r="C11" s="25" t="n">
@@ -2582,11 +2590,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c s="38" r="B13" t="s">
         <v>167</v>
       </c>
       <c r="C13" s="25" t="n">
@@ -2636,11 +2644,11 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c s="38" r="B15" t="s">
         <v>174</v>
       </c>
       <c r="C15" s="25" t="n">
@@ -2914,8 +2922,8 @@
         <v>40399.54</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A6" t="s">
         <v>203</v>
       </c>
       <c r="B6" s="29" t="n">
@@ -3493,8 +3501,8 @@
         <v>-15775.23</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+    <row ht="27" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A31" t="s">
         <v>253</v>
       </c>
       <c r="B31" s="28" t="n">
@@ -3713,7 +3721,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c s="39" r="A4" t="s">
         <v>130</v>
       </c>
       <c r="B4" s="20" t="s">
